--- a/private/planilla-plazo-fijo-2026.xlsx
+++ b/private/planilla-plazo-fijo-2026.xlsx
@@ -75,7 +75,7 @@
     <t>•  La tasa real es la que importa para tu bolsillo: lo que cobrás descontada la inflación del período. Una TNA alta puede tener tasa real negativa si la inflación fue mayor.</t>
   </si>
   <si>
-    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (22,27% al 24/09/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
+    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (20,96% al 05/10/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
   </si>
   <si>
     <t>•  Plazo fijo UVA (Com. «A» 8246 del BCRA): mínimo 90 días, precancelable desde el día 30 sin el ajuste por inflación.</t>
@@ -216,7 +216,7 @@
     <t>DATOS</t>
   </si>
   <si>
-    <t>TNA promedio de los bancos al 24/09/2026 (BCRA): 22,27%. Poné la de tu banco.</t>
+    <t>TNA promedio de los bancos al 05/10/2026 (BCRA): 20,96%. Poné la de tu banco.</t>
   </si>
   <si>
     <t>Días de cada plazo</t>
@@ -441,7 +441,7 @@
     <t>IPC Nacional del INDEC — nivel general (base diciembre 2016 = 100)</t>
   </si>
   <si>
-    <t>Serie oficial descargada el 28/09/2026 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
+    <t>Serie oficial descargada el 07/10/2026 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
   </si>
   <si>
     <t>Período</t>
@@ -1017,25 +1017,25 @@
     <t>Link</t>
   </si>
   <si>
-    <t>BCRA — Estadísticas monetarias, tasa de depósitos a 30 días (serie 12)</t>
+    <t>BCRA: Estadísticas monetarias, tasa de depósitos a 30 días (serie 12)</t>
   </si>
   <si>
     <t>https://api.bcra.gob.ar/estadisticas/v4.0/monetarias/12</t>
   </si>
   <si>
-    <t>BCRA — Comunicación «A» 8246/2025 (plazo fijo UVA: mínimo 90 días)</t>
+    <t>BCRA: Comunicación «A» 8246/2025 (plazo fijo UVA: mínimo 90 días)</t>
   </si>
   <si>
     <t>https://www.bcra.gob.ar/Pdfs/comytexord/A8246.pdf</t>
   </si>
   <si>
-    <t>BCRA — Comunicación «A» 8407 (garantía de los depósitos: $50.000.000)</t>
+    <t>BCRA: Comunicación «A» 8407 (garantía de los depósitos: $50.000.000)</t>
   </si>
   <si>
     <t>https://www.bcra.gob.ar/archivos/Pdfs/comytexord/A8407.pdf</t>
   </si>
   <si>
-    <t>INDEC — IPC Nacional, nivel general (API oficial de series de tiempo)</t>
+    <t>INDEC: IPC Nacional, nivel general (API oficial de series de tiempo)</t>
   </si>
   <si>
     <t>https://datos.gob.ar/series/api/series/?ids=148.3_INIVELNAL_DICI_M_26&amp;format=json</t>
@@ -1047,7 +1047,7 @@
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/330000-334999/332890/texact.htm</t>
   </si>
   <si>
-    <t>Planilla de calcular.ar. Serie del IPC descargada el 28/09/2026; TNA de referencia del BCRA al 24/09/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
+    <t>Planilla de calcular.ar. Serie del IPC descargada el 07/10/2026; TNA de referencia del BCRA al 05/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
   </si>
 </sst>
 </file>
@@ -2096,7 +2096,7 @@
         <v>1000000</v>
       </c>
       <c r="D15" s="13">
-        <v>22.27</v>
+        <v>20.96</v>
       </c>
       <c r="E15" s="23">
         <v>30</v>
@@ -2176,13 +2176,13 @@
         <v>52</v>
       </c>
       <c r="B16" s="21">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="C16" s="22">
         <v>2500000</v>
       </c>
       <c r="D16" s="13">
-        <v>22.27</v>
+        <v>20.96</v>
       </c>
       <c r="E16" s="23">
         <v>60</v>
@@ -4914,7 +4914,7 @@
         <v>39</v>
       </c>
       <c r="B6" s="13">
-        <v>22.27</v>
+        <v>20.96</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>64</v>
@@ -5651,7 +5651,7 @@
         <v>94</v>
       </c>
       <c r="B8" s="13">
-        <v>22.27</v>
+        <v>20.96</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -5878,7 +5878,7 @@
         <v>110</v>
       </c>
       <c r="B8" s="21">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -5886,7 +5886,7 @@
         <v>39</v>
       </c>
       <c r="B9" s="13">
-        <v>22.27</v>
+        <v>20.96</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>111</v>

--- a/private/planilla-plazo-fijo-2026.xlsx
+++ b/private/planilla-plazo-fijo-2026.xlsx
@@ -75,7 +75,7 @@
     <t>•  La tasa real es la que importa para tu bolsillo: lo que cobrás descontada la inflación del período. Una TNA alta puede tener tasa real negativa si la inflación fue mayor.</t>
   </si>
   <si>
-    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (20,96% al 05/10/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
+    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (22,6% al 06/10/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
   </si>
   <si>
     <t>•  Plazo fijo UVA (Com. «A» 8246 del BCRA): mínimo 90 días, precancelable desde el día 30 sin el ajuste por inflación.</t>
@@ -216,7 +216,7 @@
     <t>DATOS</t>
   </si>
   <si>
-    <t>TNA promedio de los bancos al 05/10/2026 (BCRA): 20,96%. Poné la de tu banco.</t>
+    <t>TNA promedio de los bancos al 06/10/2026 (BCRA): 22,6%. Poné la de tu banco.</t>
   </si>
   <si>
     <t>Días de cada plazo</t>
@@ -1047,7 +1047,7 @@
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/330000-334999/332890/texact.htm</t>
   </si>
   <si>
-    <t>Planilla de calcular.ar. Serie del IPC descargada el 07/10/2026; TNA de referencia del BCRA al 05/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
+    <t>Planilla de calcular.ar. Serie del IPC descargada el 07/10/2026; TNA de referencia del BCRA al 06/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
   </si>
 </sst>
 </file>
@@ -2096,7 +2096,7 @@
         <v>1000000</v>
       </c>
       <c r="D15" s="13">
-        <v>20.96</v>
+        <v>22.6</v>
       </c>
       <c r="E15" s="23">
         <v>30</v>
@@ -2182,7 +2182,7 @@
         <v>2500000</v>
       </c>
       <c r="D16" s="13">
-        <v>20.96</v>
+        <v>22.6</v>
       </c>
       <c r="E16" s="23">
         <v>60</v>
@@ -4914,7 +4914,7 @@
         <v>39</v>
       </c>
       <c r="B6" s="13">
-        <v>20.96</v>
+        <v>22.6</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>64</v>
@@ -5651,7 +5651,7 @@
         <v>94</v>
       </c>
       <c r="B8" s="13">
-        <v>20.96</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -5886,7 +5886,7 @@
         <v>39</v>
       </c>
       <c r="B9" s="13">
-        <v>20.96</v>
+        <v>22.6</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>111</v>

--- a/private/planilla-plazo-fijo-2026.xlsx
+++ b/private/planilla-plazo-fijo-2026.xlsx
@@ -2176,7 +2176,7 @@
         <v>52</v>
       </c>
       <c r="B16" s="21">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C16" s="22">
         <v>2500000</v>
@@ -5878,7 +5878,7 @@
         <v>110</v>
       </c>
       <c r="B8" s="21">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">

--- a/private/planilla-plazo-fijo-2026.xlsx
+++ b/private/planilla-plazo-fijo-2026.xlsx
@@ -75,7 +75,7 @@
     <t>•  La tasa real es la que importa para tu bolsillo: lo que cobrás descontada la inflación del período. Una TNA alta puede tener tasa real negativa si la inflación fue mayor.</t>
   </si>
   <si>
-    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (22,6% al 06/10/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
+    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (21,13% al 07/10/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
   </si>
   <si>
     <t>•  Plazo fijo UVA (Com. «A» 8246 del BCRA): mínimo 90 días, precancelable desde el día 30 sin el ajuste por inflación.</t>
@@ -216,7 +216,7 @@
     <t>DATOS</t>
   </si>
   <si>
-    <t>TNA promedio de los bancos al 06/10/2026 (BCRA): 22,6%. Poné la de tu banco.</t>
+    <t>TNA promedio de los bancos al 07/10/2026 (BCRA): 21,13%. Poné la de tu banco.</t>
   </si>
   <si>
     <t>Días de cada plazo</t>
@@ -1047,7 +1047,7 @@
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/330000-334999/332890/texact.htm</t>
   </si>
   <si>
-    <t>Planilla de calcular.ar. Serie del IPC descargada el 07/10/2026; TNA de referencia del BCRA al 06/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
+    <t>Planilla de calcular.ar. Serie del IPC descargada el 07/10/2026; TNA de referencia del BCRA al 07/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
   </si>
 </sst>
 </file>
@@ -2096,7 +2096,7 @@
         <v>1000000</v>
       </c>
       <c r="D15" s="13">
-        <v>22.6</v>
+        <v>21.13</v>
       </c>
       <c r="E15" s="23">
         <v>30</v>
@@ -2176,13 +2176,13 @@
         <v>52</v>
       </c>
       <c r="B16" s="21">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C16" s="22">
         <v>2500000</v>
       </c>
       <c r="D16" s="13">
-        <v>22.6</v>
+        <v>21.13</v>
       </c>
       <c r="E16" s="23">
         <v>60</v>
@@ -4914,7 +4914,7 @@
         <v>39</v>
       </c>
       <c r="B6" s="13">
-        <v>22.6</v>
+        <v>21.13</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>64</v>
@@ -5651,7 +5651,7 @@
         <v>94</v>
       </c>
       <c r="B8" s="13">
-        <v>22.6</v>
+        <v>21.13</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -5878,7 +5878,7 @@
         <v>110</v>
       </c>
       <c r="B8" s="21">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -5886,7 +5886,7 @@
         <v>39</v>
       </c>
       <c r="B9" s="13">
-        <v>22.6</v>
+        <v>21.13</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>111</v>

--- a/private/planilla-plazo-fijo-2026.xlsx
+++ b/private/planilla-plazo-fijo-2026.xlsx
@@ -2176,7 +2176,7 @@
         <v>52</v>
       </c>
       <c r="B16" s="21">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="C16" s="22">
         <v>2500000</v>
@@ -5878,7 +5878,7 @@
         <v>110</v>
       </c>
       <c r="B8" s="21">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">

--- a/private/planilla-plazo-fijo-2026.xlsx
+++ b/private/planilla-plazo-fijo-2026.xlsx
@@ -75,7 +75,7 @@
     <t>•  La tasa real es la que importa para tu bolsillo: lo que cobrás descontada la inflación del período. Una TNA alta puede tener tasa real negativa si la inflación fue mayor.</t>
   </si>
   <si>
-    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (21,13% al 07/10/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
+    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (22,3% al 08/10/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
   </si>
   <si>
     <t>•  Plazo fijo UVA (Com. «A» 8246 del BCRA): mínimo 90 días, precancelable desde el día 30 sin el ajuste por inflación.</t>
@@ -216,7 +216,7 @@
     <t>DATOS</t>
   </si>
   <si>
-    <t>TNA promedio de los bancos al 07/10/2026 (BCRA): 21,13%. Poné la de tu banco.</t>
+    <t>TNA promedio de los bancos al 08/10/2026 (BCRA): 22,3%. Poné la de tu banco.</t>
   </si>
   <si>
     <t>Días de cada plazo</t>
@@ -1047,7 +1047,7 @@
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/330000-334999/332890/texact.htm</t>
   </si>
   <si>
-    <t>Planilla de calcular.ar. Serie del IPC descargada el 07/10/2026; TNA de referencia del BCRA al 07/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
+    <t>Planilla de calcular.ar. Serie del IPC descargada el 07/10/2026; TNA de referencia del BCRA al 08/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
   </si>
 </sst>
 </file>
@@ -2096,7 +2096,7 @@
         <v>1000000</v>
       </c>
       <c r="D15" s="13">
-        <v>21.13</v>
+        <v>22.3</v>
       </c>
       <c r="E15" s="23">
         <v>30</v>
@@ -2182,7 +2182,7 @@
         <v>2500000</v>
       </c>
       <c r="D16" s="13">
-        <v>21.13</v>
+        <v>22.3</v>
       </c>
       <c r="E16" s="23">
         <v>60</v>
@@ -4914,7 +4914,7 @@
         <v>39</v>
       </c>
       <c r="B6" s="13">
-        <v>21.13</v>
+        <v>22.3</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>64</v>
@@ -5651,7 +5651,7 @@
         <v>94</v>
       </c>
       <c r="B8" s="13">
-        <v>21.13</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -5886,7 +5886,7 @@
         <v>39</v>
       </c>
       <c r="B9" s="13">
-        <v>21.13</v>
+        <v>22.3</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>111</v>

--- a/private/planilla-plazo-fijo-2026.xlsx
+++ b/private/planilla-plazo-fijo-2026.xlsx
@@ -2176,7 +2176,7 @@
         <v>52</v>
       </c>
       <c r="B16" s="21">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="C16" s="22">
         <v>2500000</v>
@@ -5878,7 +5878,7 @@
         <v>110</v>
       </c>
       <c r="B8" s="21">
-        <v>46304</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">

--- a/private/planilla-plazo-fijo-2026.xlsx
+++ b/private/planilla-plazo-fijo-2026.xlsx
@@ -75,7 +75,7 @@
     <t>•  La tasa real es la que importa para tu bolsillo: lo que cobrás descontada la inflación del período. Una TNA alta puede tener tasa real negativa si la inflación fue mayor.</t>
   </si>
   <si>
-    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (22,3% al 08/10/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
+    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (20,65% al 13/10/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
   </si>
   <si>
     <t>•  Plazo fijo UVA (Com. «A» 8246 del BCRA): mínimo 90 días, precancelable desde el día 30 sin el ajuste por inflación.</t>
@@ -216,7 +216,7 @@
     <t>DATOS</t>
   </si>
   <si>
-    <t>TNA promedio de los bancos al 08/10/2026 (BCRA): 22,3%. Poné la de tu banco.</t>
+    <t>TNA promedio de los bancos al 13/10/2026 (BCRA): 20,65%. Poné la de tu banco.</t>
   </si>
   <si>
     <t>Días de cada plazo</t>
@@ -441,7 +441,7 @@
     <t>IPC Nacional del INDEC — nivel general (base diciembre 2016 = 100)</t>
   </si>
   <si>
-    <t>Serie oficial descargada el 07/10/2026 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
+    <t>Serie oficial descargada el 15/10/2026 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
   </si>
   <si>
     <t>Período</t>
@@ -1047,7 +1047,7 @@
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/330000-334999/332890/texact.htm</t>
   </si>
   <si>
-    <t>Planilla de calcular.ar. Serie del IPC descargada el 07/10/2026; TNA de referencia del BCRA al 08/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
+    <t>Planilla de calcular.ar. Serie del IPC descargada el 15/10/2026; TNA de referencia del BCRA al 13/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
   </si>
 </sst>
 </file>
@@ -2096,7 +2096,7 @@
         <v>1000000</v>
       </c>
       <c r="D15" s="13">
-        <v>22.3</v>
+        <v>20.65</v>
       </c>
       <c r="E15" s="23">
         <v>30</v>
@@ -2176,13 +2176,13 @@
         <v>52</v>
       </c>
       <c r="B16" s="21">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="C16" s="22">
         <v>2500000</v>
       </c>
       <c r="D16" s="13">
-        <v>22.3</v>
+        <v>20.65</v>
       </c>
       <c r="E16" s="23">
         <v>60</v>
@@ -4914,7 +4914,7 @@
         <v>39</v>
       </c>
       <c r="B6" s="13">
-        <v>22.3</v>
+        <v>20.65</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>64</v>
@@ -5651,7 +5651,7 @@
         <v>94</v>
       </c>
       <c r="B8" s="13">
-        <v>22.3</v>
+        <v>20.65</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -5878,7 +5878,7 @@
         <v>110</v>
       </c>
       <c r="B8" s="21">
-        <v>46304</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -5886,7 +5886,7 @@
         <v>39</v>
       </c>
       <c r="B9" s="13">
-        <v>22.3</v>
+        <v>20.65</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>111</v>

--- a/private/planilla-plazo-fijo-2026.xlsx
+++ b/private/planilla-plazo-fijo-2026.xlsx
@@ -75,7 +75,7 @@
     <t>•  La tasa real es la que importa para tu bolsillo: lo que cobrás descontada la inflación del período. Una TNA alta puede tener tasa real negativa si la inflación fue mayor.</t>
   </si>
   <si>
-    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (20,65% al 13/10/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
+    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (20,85% al 14/10/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
   </si>
   <si>
     <t>•  Plazo fijo UVA (Com. «A» 8246 del BCRA): mínimo 90 días, precancelable desde el día 30 sin el ajuste por inflación.</t>
@@ -216,7 +216,7 @@
     <t>DATOS</t>
   </si>
   <si>
-    <t>TNA promedio de los bancos al 13/10/2026 (BCRA): 20,65%. Poné la de tu banco.</t>
+    <t>TNA promedio de los bancos al 14/10/2026 (BCRA): 20,85%. Poné la de tu banco.</t>
   </si>
   <si>
     <t>Días de cada plazo</t>
@@ -1047,7 +1047,7 @@
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/330000-334999/332890/texact.htm</t>
   </si>
   <si>
-    <t>Planilla de calcular.ar. Serie del IPC descargada el 15/10/2026; TNA de referencia del BCRA al 13/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
+    <t>Planilla de calcular.ar. Serie del IPC descargada el 15/10/2026; TNA de referencia del BCRA al 14/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
   </si>
 </sst>
 </file>
@@ -2096,7 +2096,7 @@
         <v>1000000</v>
       </c>
       <c r="D15" s="13">
-        <v>20.65</v>
+        <v>20.85</v>
       </c>
       <c r="E15" s="23">
         <v>30</v>
@@ -2176,13 +2176,13 @@
         <v>52</v>
       </c>
       <c r="B16" s="21">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C16" s="22">
         <v>2500000</v>
       </c>
       <c r="D16" s="13">
-        <v>20.65</v>
+        <v>20.85</v>
       </c>
       <c r="E16" s="23">
         <v>60</v>
@@ -4914,7 +4914,7 @@
         <v>39</v>
       </c>
       <c r="B6" s="13">
-        <v>20.65</v>
+        <v>20.85</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>64</v>
@@ -5651,7 +5651,7 @@
         <v>94</v>
       </c>
       <c r="B8" s="13">
-        <v>20.65</v>
+        <v>20.85</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -5878,7 +5878,7 @@
         <v>110</v>
       </c>
       <c r="B8" s="21">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -5886,7 +5886,7 @@
         <v>39</v>
       </c>
       <c r="B9" s="13">
-        <v>20.65</v>
+        <v>20.85</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>111</v>

--- a/private/planilla-plazo-fijo-2026.xlsx
+++ b/private/planilla-plazo-fijo-2026.xlsx
@@ -75,7 +75,7 @@
     <t>•  La tasa real es la que importa para tu bolsillo: lo que cobrás descontada la inflación del período. Una TNA alta puede tener tasa real negativa si la inflación fue mayor.</t>
   </si>
   <si>
-    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (20,85% al 14/10/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
+    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (21,74% al 15/10/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
   </si>
   <si>
     <t>•  Plazo fijo UVA (Com. «A» 8246 del BCRA): mínimo 90 días, precancelable desde el día 30 sin el ajuste por inflación.</t>
@@ -216,7 +216,7 @@
     <t>DATOS</t>
   </si>
   <si>
-    <t>TNA promedio de los bancos al 14/10/2026 (BCRA): 20,85%. Poné la de tu banco.</t>
+    <t>TNA promedio de los bancos al 15/10/2026 (BCRA): 21,74%. Poné la de tu banco.</t>
   </si>
   <si>
     <t>Días de cada plazo</t>
@@ -1047,7 +1047,7 @@
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/330000-334999/332890/texact.htm</t>
   </si>
   <si>
-    <t>Planilla de calcular.ar. Serie del IPC descargada el 15/10/2026; TNA de referencia del BCRA al 14/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
+    <t>Planilla de calcular.ar. Serie del IPC descargada el 15/10/2026; TNA de referencia del BCRA al 15/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
   </si>
 </sst>
 </file>
@@ -2096,7 +2096,7 @@
         <v>1000000</v>
       </c>
       <c r="D15" s="13">
-        <v>20.85</v>
+        <v>21.74</v>
       </c>
       <c r="E15" s="23">
         <v>30</v>
@@ -2176,13 +2176,13 @@
         <v>52</v>
       </c>
       <c r="B16" s="21">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C16" s="22">
         <v>2500000</v>
       </c>
       <c r="D16" s="13">
-        <v>20.85</v>
+        <v>21.74</v>
       </c>
       <c r="E16" s="23">
         <v>60</v>
@@ -4914,7 +4914,7 @@
         <v>39</v>
       </c>
       <c r="B6" s="13">
-        <v>20.85</v>
+        <v>21.74</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>64</v>
@@ -5651,7 +5651,7 @@
         <v>94</v>
       </c>
       <c r="B8" s="13">
-        <v>20.85</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -5878,7 +5878,7 @@
         <v>110</v>
       </c>
       <c r="B8" s="21">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -5886,7 +5886,7 @@
         <v>39</v>
       </c>
       <c r="B9" s="13">
-        <v>20.85</v>
+        <v>21.74</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>111</v>

--- a/private/planilla-plazo-fijo-2026.xlsx
+++ b/private/planilla-plazo-fijo-2026.xlsx
@@ -75,7 +75,7 @@
     <t>•  La tasa real es la que importa para tu bolsillo: lo que cobrás descontada la inflación del período. Una TNA alta puede tener tasa real negativa si la inflación fue mayor.</t>
   </si>
   <si>
-    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (21,74% al 15/10/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
+    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (22,66% al 16/10/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
   </si>
   <si>
     <t>•  Plazo fijo UVA (Com. «A» 8246 del BCRA): mínimo 90 días, precancelable desde el día 30 sin el ajuste por inflación.</t>
@@ -216,7 +216,7 @@
     <t>DATOS</t>
   </si>
   <si>
-    <t>TNA promedio de los bancos al 15/10/2026 (BCRA): 21,74%. Poné la de tu banco.</t>
+    <t>TNA promedio de los bancos al 16/10/2026 (BCRA): 22,66%. Poné la de tu banco.</t>
   </si>
   <si>
     <t>Días de cada plazo</t>
@@ -1047,7 +1047,7 @@
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/330000-334999/332890/texact.htm</t>
   </si>
   <si>
-    <t>Planilla de calcular.ar. Serie del IPC descargada el 15/10/2026; TNA de referencia del BCRA al 15/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
+    <t>Planilla de calcular.ar. Serie del IPC descargada el 15/10/2026; TNA de referencia del BCRA al 16/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
   </si>
 </sst>
 </file>
@@ -2096,7 +2096,7 @@
         <v>1000000</v>
       </c>
       <c r="D15" s="13">
-        <v>21.74</v>
+        <v>22.66</v>
       </c>
       <c r="E15" s="23">
         <v>30</v>
@@ -2176,13 +2176,13 @@
         <v>52</v>
       </c>
       <c r="B16" s="21">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C16" s="22">
         <v>2500000</v>
       </c>
       <c r="D16" s="13">
-        <v>21.74</v>
+        <v>22.66</v>
       </c>
       <c r="E16" s="23">
         <v>60</v>
@@ -4914,7 +4914,7 @@
         <v>39</v>
       </c>
       <c r="B6" s="13">
-        <v>21.74</v>
+        <v>22.66</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>64</v>
@@ -5651,7 +5651,7 @@
         <v>94</v>
       </c>
       <c r="B8" s="13">
-        <v>21.74</v>
+        <v>22.66</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -5878,7 +5878,7 @@
         <v>110</v>
       </c>
       <c r="B8" s="21">
-        <v>46311</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -5886,7 +5886,7 @@
         <v>39</v>
       </c>
       <c r="B9" s="13">
-        <v>21.74</v>
+        <v>22.66</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>111</v>

--- a/private/planilla-plazo-fijo-2026.xlsx
+++ b/private/planilla-plazo-fijo-2026.xlsx
@@ -2176,7 +2176,7 @@
         <v>52</v>
       </c>
       <c r="B16" s="21">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C16" s="22">
         <v>2500000</v>
@@ -5878,7 +5878,7 @@
         <v>110</v>
       </c>
       <c r="B8" s="21">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">

--- a/private/planilla-plazo-fijo-2026.xlsx
+++ b/private/planilla-plazo-fijo-2026.xlsx
@@ -75,7 +75,7 @@
     <t>•  La tasa real es la que importa para tu bolsillo: lo que cobrás descontada la inflación del período. Una TNA alta puede tener tasa real negativa si la inflación fue mayor.</t>
   </si>
   <si>
-    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (22,66% al 16/10/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
+    <t>•  TNA de referencia: el promedio que pagan los bancos por depósitos a 30 días, publicado por el BCRA (22,41% al 20/10/2026). Tu banco puede pagar más o menos: cargá siempre la tuya.</t>
   </si>
   <si>
     <t>•  Plazo fijo UVA (Com. «A» 8246 del BCRA): mínimo 90 días, precancelable desde el día 30 sin el ajuste por inflación.</t>
@@ -216,7 +216,7 @@
     <t>DATOS</t>
   </si>
   <si>
-    <t>TNA promedio de los bancos al 16/10/2026 (BCRA): 22,66%. Poné la de tu banco.</t>
+    <t>TNA promedio de los bancos al 20/10/2026 (BCRA): 22,41%. Poné la de tu banco.</t>
   </si>
   <si>
     <t>Días de cada plazo</t>
@@ -1047,7 +1047,7 @@
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/330000-334999/332890/texact.htm</t>
   </si>
   <si>
-    <t>Planilla de calcular.ar. Serie del IPC descargada el 15/10/2026; TNA de referencia del BCRA al 16/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
+    <t>Planilla de calcular.ar. Serie del IPC descargada el 15/10/2026; TNA de referencia del BCRA al 20/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
   </si>
 </sst>
 </file>
@@ -2096,7 +2096,7 @@
         <v>1000000</v>
       </c>
       <c r="D15" s="13">
-        <v>22.66</v>
+        <v>22.41</v>
       </c>
       <c r="E15" s="23">
         <v>30</v>
@@ -2176,13 +2176,13 @@
         <v>52</v>
       </c>
       <c r="B16" s="21">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C16" s="22">
         <v>2500000</v>
       </c>
       <c r="D16" s="13">
-        <v>22.66</v>
+        <v>22.41</v>
       </c>
       <c r="E16" s="23">
         <v>60</v>
@@ -4914,7 +4914,7 @@
         <v>39</v>
       </c>
       <c r="B6" s="13">
-        <v>22.66</v>
+        <v>22.41</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>64</v>
@@ -5651,7 +5651,7 @@
         <v>94</v>
       </c>
       <c r="B8" s="13">
-        <v>22.66</v>
+        <v>22.41</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -5878,7 +5878,7 @@
         <v>110</v>
       </c>
       <c r="B8" s="21">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -5886,7 +5886,7 @@
         <v>39</v>
       </c>
       <c r="B9" s="13">
-        <v>22.66</v>
+        <v>22.41</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>111</v>

--- a/private/planilla-plazo-fijo-2026.xlsx
+++ b/private/planilla-plazo-fijo-2026.xlsx
@@ -441,7 +441,7 @@
     <t>IPC Nacional del INDEC — nivel general (base diciembre 2016 = 100)</t>
   </si>
   <si>
-    <t>Serie oficial descargada el 15/10/2026 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
+    <t>Serie oficial descargada el 23/10/2026 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
   </si>
   <si>
     <t>Período</t>
@@ -1047,7 +1047,7 @@
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/330000-334999/332890/texact.htm</t>
   </si>
   <si>
-    <t>Planilla de calcular.ar. Serie del IPC descargada el 15/10/2026; TNA de referencia del BCRA al 20/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
+    <t>Planilla de calcular.ar. Serie del IPC descargada el 23/10/2026; TNA de referencia del BCRA al 20/10/2026. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
   </si>
 </sst>
 </file>
@@ -2176,7 +2176,7 @@
         <v>52</v>
       </c>
       <c r="B16" s="21">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C16" s="22">
         <v>2500000</v>
@@ -5878,7 +5878,7 @@
         <v>110</v>
       </c>
       <c r="B8" s="21">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
